--- a/data/test-data.xlsx
+++ b/data/test-data.xlsx
@@ -8,20 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audtejas\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6E5DE0-7F73-464F-92E3-1E7EFCA77897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F025147-75BA-4205-9736-C20A584DAD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRM" sheetId="1" r:id="rId1"/>
-    <sheet name="FlowConfig" sheetId="2" r:id="rId2"/>
+    <sheet name="CRM_Mod" sheetId="16" r:id="rId2"/>
+    <sheet name="HPORDM" sheetId="17" r:id="rId3"/>
+    <sheet name="term_deposits" sheetId="18" r:id="rId4"/>
+    <sheet name="FlowConfig" sheetId="2" r:id="rId5"/>
+    <sheet name="SavingsAccountData" sheetId="3" r:id="rId6"/>
+    <sheet name="CurrentAccountData" sheetId="4" r:id="rId7"/>
+    <sheet name="SavingsAccountModifyData" sheetId="5" r:id="rId8"/>
+    <sheet name="SavingsAccountModifyVerifyData" sheetId="6" r:id="rId9"/>
+    <sheet name="SavingsAccountRelatedPartyData" sheetId="7" r:id="rId10"/>
+    <sheet name="SavingsAccountDelRelPartyData" sheetId="8" r:id="rId11"/>
+    <sheet name="SavingsAccountDelRelPartyVerify" sheetId="9" r:id="rId12"/>
+    <sheet name="SavingsAccountFreezeData" sheetId="10" r:id="rId13"/>
+    <sheet name="SavingsAccountUnfreezeData" sheetId="11" r:id="rId14"/>
+    <sheet name="SavingsAccountFreezeVerifyData" sheetId="12" r:id="rId15"/>
+    <sheet name="CurrentAccountModifyData" sheetId="13" r:id="rId16"/>
+    <sheet name="CurrentAccountModifyVerifyData" sheetId="14" r:id="rId17"/>
+    <sheet name="TransferMaintenanceData" sheetId="15" r:id="rId18"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="648">
   <si>
     <t>instance</t>
   </si>
@@ -347,7 +363,7 @@
     <t>MR</t>
   </si>
   <si>
-    <t>SSMITH</t>
+    <t>Kevin</t>
   </si>
   <si>
     <t>01/01/2023</t>
@@ -668,10 +684,1303 @@
     <t>corporate</t>
   </si>
   <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Christ</t>
+    <t>currentAccount</t>
+  </si>
+  <si>
+    <t>tests/Finacle/currentaccount/currentaccountcreation.spec.ts</t>
+  </si>
+  <si>
+    <t>CurrentAccountData</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>currentAccounts</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>tests/Finacle/currentaccount/currentaccountcreationverify.spec.ts</t>
+  </si>
+  <si>
+    <t>savingsAccount</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/savingsaccountcreation.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountData</t>
+  </si>
+  <si>
+    <t>savings</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/savingsaccountcreationverify.spec.ts</t>
+  </si>
+  <si>
+    <t>savingsAccounts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/savingsaccountmodification.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountModifyData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/savingsaccountmodifyverification.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountModifyVerifyData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/addrelatedpartydetailsforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountRelatedPartyData</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/addrelatedpartyverificationforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/DeleteRelatedpartydetailsforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountDelRelPartyData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/verifyDeletedRelatedpartydetailsforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountDelRelPartyVerify</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/accountfreezeforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountFreezeData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/AcFreezeverificationforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountFreezeVerifyData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/savingsaccount/accountunfreezeforsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>SavingsAccountUnfreezeData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/currentaccount/currentaccountmodification.spec.ts</t>
+  </si>
+  <si>
+    <t>CurrentAccountModifyData</t>
+  </si>
+  <si>
+    <t>tests/Finacle/currentaccount/currentaccountmodifyverification.spec.ts</t>
+  </si>
+  <si>
+    <t>CurrentAccountModifyVerifyData</t>
+  </si>
+  <si>
+    <t>transferMaintenance</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/accountfundingcurrentaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>TransferMaintenanceData</t>
+  </si>
+  <si>
+    <t>accountId</t>
+  </si>
+  <si>
+    <t>transfer</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/accountfundingsavingsaccount.spec.ts</t>
+  </si>
+  <si>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/cashdeposit.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/cashwithdrawal.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/accountfundingverification.spec.ts</t>
+  </si>
+  <si>
+    <t>transactionIds</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/transfermaintainenceverification.spec.ts</t>
+  </si>
+  <si>
+    <t>transactionId</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/HACLIsp.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/transfermaintainence/spHADVC.spec.ts</t>
+  </si>
+  <si>
+    <t>schemeCode</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>cifCode</t>
+  </si>
+  <si>
+    <t>functionOption</t>
+  </si>
+  <si>
+    <t>dispatchMode</t>
+  </si>
+  <si>
+    <t>SVREG</t>
+  </si>
+  <si>
+    <t>0005000599</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>SVREG NEWGEN customer</t>
+  </si>
+  <si>
+    <t>OPBUS</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>OPPRE</t>
+  </si>
+  <si>
+    <t>OPELT</t>
+  </si>
+  <si>
+    <t>OPCOR</t>
+  </si>
+  <si>
+    <t>SVNOW</t>
+  </si>
+  <si>
+    <t>OPBNW</t>
+  </si>
+  <si>
+    <t>SVSTF</t>
+  </si>
+  <si>
+    <t>SVIRK</t>
+  </si>
+  <si>
+    <t>SVGRD</t>
+  </si>
+  <si>
+    <t>SVMAS</t>
+  </si>
+  <si>
+    <t>SVSEN</t>
+  </si>
+  <si>
+    <t>SVPRE</t>
+  </si>
+  <si>
+    <t>OPCNW</t>
+  </si>
+  <si>
+    <t>OPENW</t>
+  </si>
+  <si>
+    <t>CACOB</t>
+  </si>
+  <si>
+    <t>CACOC</t>
+  </si>
+  <si>
+    <t>CACOE</t>
+  </si>
+  <si>
+    <t>CAMAS</t>
+  </si>
+  <si>
+    <t>CAREG</t>
+  </si>
+  <si>
+    <t>CASEN</t>
+  </si>
+  <si>
+    <t>CASTF</t>
+  </si>
+  <si>
+    <t>0002000305</t>
+  </si>
+  <si>
+    <t>accountStatus</t>
+  </si>
+  <si>
+    <t>testLabel</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>HACM - modify savings account dispatch mode</t>
+  </si>
+  <si>
+    <t>HACM - modify savings account dispatch mode - instance 2</t>
+  </si>
+  <si>
+    <t>HACM - modify savings account dispatch mode - instance 3</t>
+  </si>
+  <si>
+    <t>visitDocumentTab</t>
+  </si>
+  <si>
+    <t>HACM - verify savings account modification</t>
+  </si>
+  <si>
+    <t>HACM - verify savings account modification - instance 2</t>
+  </si>
+  <si>
+    <t>HACM - verify savings account modification - instance 3</t>
+  </si>
+  <si>
+    <t>relatedPartyCif</t>
+  </si>
+  <si>
+    <t>relationType</t>
+  </si>
+  <si>
+    <t>relationCode</t>
+  </si>
+  <si>
+    <t>7500001476</t>
+  </si>
+  <si>
+    <t>0002012248</t>
+  </si>
+  <si>
+    <t>Joint Holder</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>HACM - add related party to savings account</t>
+  </si>
+  <si>
+    <t>0002012249</t>
+  </si>
+  <si>
+    <t>7600000160</t>
+  </si>
+  <si>
+    <t>HACM - delete related party from account</t>
+  </si>
+  <si>
+    <t>HACM - verify deleted related party for savings account</t>
+  </si>
+  <si>
+    <t>freezeCode</t>
+  </si>
+  <si>
+    <t>freezeReasonCode</t>
+  </si>
+  <si>
+    <t>7710003367</t>
+  </si>
+  <si>
+    <t>Total Freeze</t>
+  </si>
+  <si>
+    <t>31015</t>
+  </si>
+  <si>
+    <t>HAFSM - mark total freeze on savings account</t>
+  </si>
+  <si>
+    <t>HAFSM - unfreeze savings account</t>
+  </si>
+  <si>
+    <t>HAFSM - verify freeze on savings account</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>HACM - modify current account dispatch mode and A/c status - instance 1</t>
+  </si>
+  <si>
+    <t>HACM - modify current account dispatch mode and A/c status - instance 2</t>
+  </si>
+  <si>
+    <t>HACM - modify current account dispatch mode and A/c status - instance 3</t>
+  </si>
+  <si>
+    <t>HACM - verify current account modification - instance 1</t>
+  </si>
+  <si>
+    <t>HACM - verify current account modification - instance 2</t>
+  </si>
+  <si>
+    <t>HACM - verify current account modification - instance 3</t>
+  </si>
+  <si>
+    <t>testType</t>
+  </si>
+  <si>
+    <t>menuCode</t>
+  </si>
+  <si>
+    <t>debitAccount</t>
+  </si>
+  <si>
+    <t>creditAccount</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>tranTypeSubType</t>
+  </si>
+  <si>
+    <t>secondaryAmount</t>
+  </si>
+  <si>
+    <t>partTranType</t>
+  </si>
+  <si>
+    <t>accountFundingCurrent</t>
+  </si>
+  <si>
+    <t>HTM - transfer maintenance (post by part transaction)</t>
+  </si>
+  <si>
+    <t>HTM</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>7600000172</t>
+  </si>
+  <si>
+    <t>6000087527</t>
+  </si>
+  <si>
+    <t>T/CI</t>
+  </si>
+  <si>
+    <t>savingsFunding</t>
+  </si>
+  <si>
+    <t>6000123165</t>
+  </si>
+  <si>
+    <t>4600000119</t>
+  </si>
+  <si>
+    <t>serial245</t>
+  </si>
+  <si>
+    <t>Serial 245 - HTM Post by Part Transaction checkbox selects all</t>
+  </si>
+  <si>
+    <t>serial261</t>
+  </si>
+  <si>
+    <t>Serial 261 - HTM Debit/credit order on modify</t>
+  </si>
+  <si>
+    <t>cashDeposit</t>
+  </si>
+  <si>
+    <t>HCASHDEP - post and verify cash deposit</t>
+  </si>
+  <si>
+    <t>HCASHDEP</t>
+  </si>
+  <si>
+    <t>100.00</t>
+  </si>
+  <si>
+    <t>C/NR - Cash/Normal Receipt</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>6000197087</t>
+  </si>
+  <si>
+    <t>cashWithdrawal</t>
+  </si>
+  <si>
+    <t>HCASHWD - post and verify cash withdrawal</t>
+  </si>
+  <si>
+    <t>HCASHWD</t>
+  </si>
+  <si>
+    <t>C/NP - Cash/Normal Payment</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>accountFundingVerification</t>
+  </si>
+  <si>
+    <t>HTM - transfer maintenance verification</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>9200000593</t>
+  </si>
+  <si>
+    <t>transferMaintenanceVerification</t>
+  </si>
+  <si>
+    <t>HACLIsp</t>
+  </si>
+  <si>
+    <t>HACLIsp - Complete maker/verifier/narrative flow</t>
+  </si>
+  <si>
+    <t>spHADVC</t>
+  </si>
+  <si>
+    <t>HADVC - report queue generated and criteria reset for account 7500001466</t>
+  </si>
+  <si>
+    <t>HADVC</t>
+  </si>
+  <si>
+    <t>7500001466</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Clara</t>
+  </si>
+  <si>
+    <t>23/9/1990</t>
+  </si>
+  <si>
+    <t>modification.fallbackCifId</t>
+  </si>
+  <si>
+    <t>modification.lastName</t>
+  </si>
+  <si>
+    <t>modification.address.type</t>
+  </si>
+  <si>
+    <t>modification.address.houseNo</t>
+  </si>
+  <si>
+    <t>modification.address.streetNo</t>
+  </si>
+  <si>
+    <t>modification.address.streetName</t>
+  </si>
+  <si>
+    <t>modification.address.postalCode</t>
+  </si>
+  <si>
+    <t>modification.address.state</t>
+  </si>
+  <si>
+    <t>modification.address.stateCode</t>
+  </si>
+  <si>
+    <t>modification.address.city</t>
+  </si>
+  <si>
+    <t>modification.address.country</t>
+  </si>
+  <si>
+    <t>modification.address.countryCode</t>
+  </si>
+  <si>
+    <t>modification.phone.type</t>
+  </si>
+  <si>
+    <t>modification.phone.phoneNo</t>
+  </si>
+  <si>
+    <t>modification.processName</t>
+  </si>
+  <si>
+    <t>otherBankDetails.fallbackCifId</t>
+  </si>
+  <si>
+    <t>otherBankDetails.retailFallbackCifId</t>
+  </si>
+  <si>
+    <t>otherBankDetails.bankName</t>
+  </si>
+  <si>
+    <t>otherBankDetails.branchName</t>
+  </si>
+  <si>
+    <t>otherBankDetails.productCategory</t>
+  </si>
+  <si>
+    <t>otherBankDetails.accountId</t>
+  </si>
+  <si>
+    <t>otherBankDetails.channel</t>
+  </si>
+  <si>
+    <t>otherBankDetails.addressLine1</t>
+  </si>
+  <si>
+    <t>otherBankDetails.city</t>
+  </si>
+  <si>
+    <t>otherBankDetails.state</t>
+  </si>
+  <si>
+    <t>otherBankDetails.country</t>
+  </si>
+  <si>
+    <t>modification.cifId</t>
+  </si>
+  <si>
+    <t>modification.otherBank.bankName</t>
+  </si>
+  <si>
+    <t>modification.otherBank.branchName</t>
+  </si>
+  <si>
+    <t>modification.otherBank.productCategory</t>
+  </si>
+  <si>
+    <t>modification.otherBank.accountId</t>
+  </si>
+  <si>
+    <t>modification.otherBank.channel</t>
+  </si>
+  <si>
+    <t>modification.otherBank.addressLine1</t>
+  </si>
+  <si>
+    <t>modification.otherBank.city</t>
+  </si>
+  <si>
+    <t>modification.otherBank.state</t>
+  </si>
+  <si>
+    <t>modification.otherBank.country</t>
+  </si>
+  <si>
+    <t>0002000033</t>
+  </si>
+  <si>
+    <t>JAMES</t>
+  </si>
+  <si>
+    <t>BLOCK NO 13</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>HM STREET</t>
+  </si>
+  <si>
+    <t>531310</t>
+  </si>
+  <si>
+    <t>CALIFORNIA</t>
+  </si>
+  <si>
+    <t>US005</t>
+  </si>
+  <si>
+    <t>JAFFREY</t>
+  </si>
+  <si>
+    <t>MOBILE NUMBER 1</t>
+  </si>
+  <si>
+    <t>9132345678</t>
+  </si>
+  <si>
+    <t>CIFCustomerKYCApproval</t>
+  </si>
+  <si>
+    <t>CLARIEN BANK LIMITED</t>
+  </si>
+  <si>
+    <t>CLARIEN TRUST MICROGEN</t>
+  </si>
+  <si>
+    <t>666666666</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>SYENT STREET 08</t>
+  </si>
+  <si>
+    <t>AFORE</t>
+  </si>
+  <si>
+    <t>14-126</t>
+  </si>
+  <si>
+    <t>14A</t>
+  </si>
+  <si>
+    <t>DAVIDS STREET</t>
+  </si>
+  <si>
+    <t>PI 09</t>
+  </si>
+  <si>
+    <t>WORK PHONE 1</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>88888888</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>sharedKey</t>
+  </si>
+  <si>
+    <t>menuOption</t>
+  </si>
+  <si>
+    <t>function</t>
+  </si>
+  <si>
+    <t>beneficiaryAddressType</t>
+  </si>
+  <si>
+    <t>beneficiaryAccountId</t>
+  </si>
+  <si>
+    <t>beneficiaryName</t>
+  </si>
+  <si>
+    <t>beneficiaryAddress</t>
+  </si>
+  <si>
+    <t>beneficiaryCountry</t>
+  </si>
+  <si>
+    <t>institutionAddressType</t>
+  </si>
+  <si>
+    <t>bic</t>
+  </si>
+  <si>
+    <t>bankCode</t>
+  </si>
+  <si>
+    <t>branchCode</t>
+  </si>
+  <si>
+    <t>paymentMethod</t>
+  </si>
+  <si>
+    <t>chargeOption</t>
+  </si>
+  <si>
+    <t>paymentProduct</t>
+  </si>
+  <si>
+    <t>needsUsdPopup</t>
+  </si>
+  <si>
+    <t>rateCode</t>
+  </si>
+  <si>
+    <t>beneficiaryBic</t>
+  </si>
+  <si>
+    <t>beneficiaryBankCode</t>
+  </si>
+  <si>
+    <t>beneficiaryBranchCode</t>
+  </si>
+  <si>
+    <t>paymentorder</t>
+  </si>
+  <si>
+    <t>Flow 1 - SWIFT FCC BMD to JPY</t>
+  </si>
+  <si>
+    <t>paymentOrderIdSwiftFccJpy</t>
+  </si>
+  <si>
+    <t>HPORDM</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>121241242132</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>IN RERW</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>NLICJP22XXX</t>
+  </si>
+  <si>
+    <t>NLICJP</t>
+  </si>
+  <si>
+    <t>22XXX</t>
+  </si>
+  <si>
+    <t>SWIFT</t>
+  </si>
+  <si>
+    <t>OUR</t>
+  </si>
+  <si>
+    <t>customer transfer</t>
+  </si>
+  <si>
+    <t>TTB</t>
+  </si>
+  <si>
+    <t>Flow 1 - SWIFT FCC BMD to AUD</t>
+  </si>
+  <si>
+    <t>paymentOrderIdSwiftFccAud</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>6000001361</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>JPMSAU2103M</t>
+  </si>
+  <si>
+    <t>JPMSAU</t>
+  </si>
+  <si>
+    <t>2103M</t>
+  </si>
+  <si>
+    <t>Flow 1 - SWIFT FCC BMD to GBP</t>
+  </si>
+  <si>
+    <t>paymentOrderIdSwiftFccGbp</t>
+  </si>
+  <si>
+    <t>1213131331</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>LOYDGB21004</t>
+  </si>
+  <si>
+    <t>LOYDGB</t>
+  </si>
+  <si>
+    <t>21004</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH BMD to BMD</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAch</t>
+  </si>
+  <si>
+    <t>7010003820</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>1468907</t>
+  </si>
+  <si>
+    <t>50601006</t>
+  </si>
+  <si>
+    <t>BCBBM</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH FCC BMD to USD</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc</t>
+  </si>
+  <si>
+    <t>010247526001</t>
+  </si>
+  <si>
+    <t>Anna Evelyn Carr</t>
+  </si>
+  <si>
+    <t>14140 Abbington Avenue</t>
+  </si>
+  <si>
+    <t>50601002</t>
+  </si>
+  <si>
+    <t>BBDABM</t>
+  </si>
+  <si>
+    <t>HMXXX</t>
+  </si>
+  <si>
+    <t>HSBUS</t>
+  </si>
+  <si>
+    <t>Flow 1 - SWIFT FCC BMD to USD</t>
+  </si>
+  <si>
+    <t>paymentOrderIdSwiftFcc</t>
+  </si>
+  <si>
+    <t>Flow 1 - BMD TO BMD to Butterfield bank</t>
+  </si>
+  <si>
+    <t>6000270768</t>
+  </si>
+  <si>
+    <t>232244242</t>
+  </si>
+  <si>
+    <t>BMENR BERUMUDA</t>
+  </si>
+  <si>
+    <t>50601001</t>
+  </si>
+  <si>
+    <t>BNTBBM</t>
+  </si>
+  <si>
+    <t>NTBBM</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH BMD to USD to HSBC Bank</t>
+  </si>
+  <si>
+    <t>2432422424</t>
+  </si>
+  <si>
+    <t>TESTING</t>
+  </si>
+  <si>
+    <t>BERMUDA SOUTH PENRITH</t>
+  </si>
+  <si>
+    <t>58401002</t>
+  </si>
+  <si>
+    <t>Flow 1 - SWIFT BMD TO CAD</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TEST HELOT</t>
+  </si>
+  <si>
+    <t>GSCICA91XXX</t>
+  </si>
+  <si>
+    <t>GSCICA</t>
+  </si>
+  <si>
+    <t>91XXX</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc1</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH BMD TO BMD to HSBC bank</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc2</t>
+  </si>
+  <si>
+    <t>HSBBM</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH BMD TO USD to Butterfield bank</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc3</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>58401001</t>
+  </si>
+  <si>
+    <t>NTBUS</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH USD TO USD to HSBC bank</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc5</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH USD TO BMD to HSBC bank</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc6</t>
+  </si>
+  <si>
+    <t>Flow 1 - ACH USD TO USD to Butterfield bank</t>
+  </si>
+  <si>
+    <t>paymentOrderIdAchFcc7</t>
+  </si>
+  <si>
+    <t>7500001556</t>
+  </si>
+  <si>
+    <t>Flow 9 - SWIFT FCC USD to GBP</t>
+  </si>
+  <si>
+    <t>Flow 9 - SWIFT USD to USD</t>
+  </si>
+  <si>
+    <t>paymentOrderIdSwiftUsd</t>
+  </si>
+  <si>
+    <t>BPBKBM</t>
+  </si>
+  <si>
+    <t>Flow 9 - SWIFT USD to CAD</t>
+  </si>
+  <si>
+    <t>paymentOrderIdSwiftFccCad</t>
+  </si>
+  <si>
+    <t>glSubHeadCode</t>
+  </si>
+  <si>
+    <t>depositAmount</t>
+  </si>
+  <si>
+    <t>depositPeriodMonths</t>
+  </si>
+  <si>
+    <t>repaymentAccountId</t>
+  </si>
+  <si>
+    <t>operativeSbAccount</t>
+  </si>
+  <si>
+    <t>modeOfOperation</t>
+  </si>
+  <si>
+    <t>schemeCodes</t>
+  </si>
+  <si>
+    <t>depositAmountOverrides</t>
+  </si>
+  <si>
+    <t>screens</t>
+  </si>
+  <si>
+    <t>modificationAccountId</t>
+  </si>
+  <si>
+    <t>verificationAccountId</t>
+  </si>
+  <si>
+    <t>newDepositPeriodMonths</t>
+  </si>
+  <si>
+    <t>newDepositPeriodDays</t>
+  </si>
+  <si>
+    <t>partialClosureScreenCode</t>
+  </si>
+  <si>
+    <t>partialClosureFunctionOption</t>
+  </si>
+  <si>
+    <t>partialClosureWithdrawalAmount</t>
+  </si>
+  <si>
+    <t>partialClosureVerificationScreenCode</t>
+  </si>
+  <si>
+    <t>partialClosureVerificationFunctionOption</t>
+  </si>
+  <si>
+    <t>creditFrozenClosureAccountId</t>
+  </si>
+  <si>
+    <t>renewalAccountId</t>
+  </si>
+  <si>
+    <t>renewalScreenCode</t>
+  </si>
+  <si>
+    <t>renewalVerificationAccountId</t>
+  </si>
+  <si>
+    <t>renewalDetails</t>
+  </si>
+  <si>
+    <t>spflowAccountId</t>
+  </si>
+  <si>
+    <t>spflowInterestOutflowStartDate</t>
+  </si>
+  <si>
+    <t>spflowModifyScreen</t>
+  </si>
+  <si>
+    <t>spflowVerifyScreen</t>
+  </si>
+  <si>
+    <t>spflowInquiryScreen</t>
+  </si>
+  <si>
+    <t>htditciScreenCode</t>
+  </si>
+  <si>
+    <t>relatedPartyAccountId</t>
+  </si>
+  <si>
+    <t>relatedPartyRelationType</t>
+  </si>
+  <si>
+    <t>relatedPartyRelationCode</t>
+  </si>
+  <si>
+    <t>relatedPartyCifCode</t>
+  </si>
+  <si>
+    <t>relatedPartyTestLabel</t>
+  </si>
+  <si>
+    <t>partialClosureAccountId</t>
+  </si>
+  <si>
+    <t>prematureClosureAccountId</t>
+  </si>
+  <si>
+    <t>termdeposit</t>
+  </si>
+  <si>
+    <t>Term Deposit - consolidated data</t>
+  </si>
+  <si>
+    <t>termDepositData</t>
+  </si>
+  <si>
+    <t>HOAACTD</t>
+  </si>
+  <si>
+    <t>40300</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>post</t>
+  </si>
+  <si>
+    <t>["TDGNH"]</t>
+  </si>
+  <si>
+    <t>{"TDSPI":"10","TDSWH":"10","TDSWM":"10","TDSWQ":"10","TDSWZ":"10"}</t>
+  </si>
+  <si>
+    <t>{"create":"HOAACTD","modify":"HOAACMTD","verify":"HOAACVTD","inquiry":"HACMTD","partialClosure":"HCAACTD","partialClosureVerify":"HCAACVTD"}</t>
+  </si>
+  <si>
+    <t>9200000614</t>
+  </si>
+  <si>
+    <t>9200000634</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>HCAACTD</t>
+  </si>
+  <si>
+    <t>Z-close</t>
+  </si>
+  <si>
+    <t>HCAACVTD</t>
+  </si>
+  <si>
+    <t>V-Verify</t>
+  </si>
+  <si>
+    <t>9200000641</t>
+  </si>
+  <si>
+    <t>9200000604</t>
+  </si>
+  <si>
+    <t>HTDREN</t>
+  </si>
+  <si>
+    <t>9200000670</t>
+  </si>
+  <si>
+    <t>{"renewalPeriodMonths":"","renewalPeriodDays":"","printRenewalConfirmation":""}</t>
+  </si>
+  <si>
+    <t>9200000658</t>
+  </si>
+  <si>
+    <t>30-08-2026</t>
+  </si>
+  <si>
+    <t>HOAACMTD</t>
+  </si>
+  <si>
+    <t>HOAACVTD</t>
+  </si>
+  <si>
+    <t>HACMTD</t>
+  </si>
+  <si>
+    <t>HTDITCI</t>
+  </si>
+  <si>
+    <t>9200000618</t>
+  </si>
+  <si>
+    <t>HOAACTD - create term deposit accounts for all schemes</t>
+  </si>
+  <si>
+    <t>HOAACMTD - add related party details to term deposit account</t>
+  </si>
+  <si>
+    <t>crmCIFModification</t>
+  </si>
+  <si>
+    <t>tests/Finacle/crmCIFRetail/combinedcifmodification_flow.spec.ts</t>
+  </si>
+  <si>
+    <t>CRM_Mod</t>
+  </si>
+  <si>
+    <t>tests/Finacle/paymentorder/hpordm-remittance.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositscreation.spec.ts</t>
+  </si>
+  <si>
+    <t>term_deposits</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsmodification.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/addrelatedpartydetailsfortermdeposits.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/deleterelatedpartydetailsfortermdeposits.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/verifydeletedrelatedpartydetailsfortermdeposits.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositspartialclosure.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositspartialclosureverification.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsprematureclosure.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsprematureclosureverification.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsrenewal.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsrenewalverification.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsspcreditfrozen.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositsspflow.spec.ts</t>
+  </si>
+  <si>
+    <t>tests/Finacle/Termdeposits/termdepositssphtditci.spec.ts</t>
   </si>
 </sst>
 </file>
@@ -1050,9 +2359,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DC3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="9.08203125" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" customWidth="1"/>
+    <col min="100" max="100" width="19.4140625" customWidth="1"/>
+    <col min="101" max="101" width="21.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:107" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:107" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1375,7 +2690,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:107" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1383,19 +2698,19 @@
         <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>382</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>381</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="1">
-        <v>26665</v>
+        <v>383</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -1698,7 +3013,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:107" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:107" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2024,17 +3339,3500 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:DC1 A3:DC3 A2:B2 H2:DC2 F2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:DC1 A3:DC3 A2:B2 H2:DC2 E2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:G4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M1" t="s">
+        <v>343</v>
+      </c>
+      <c r="N1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" t="s">
+        <v>352</v>
+      </c>
+      <c r="I4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H5" t="s">
+        <v>352</v>
+      </c>
+      <c r="I5" t="s">
+        <v>353</v>
+      </c>
+      <c r="J5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" t="s">
+        <v>361</v>
+      </c>
+      <c r="K6" t="s">
+        <v>362</v>
+      </c>
+      <c r="M6" t="s">
+        <v>363</v>
+      </c>
+      <c r="N6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C7" t="s">
+        <v>366</v>
+      </c>
+      <c r="D7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" t="s">
+        <v>361</v>
+      </c>
+      <c r="K7" t="s">
+        <v>368</v>
+      </c>
+      <c r="M7" t="s">
+        <v>369</v>
+      </c>
+      <c r="N7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E8" t="s">
+        <v>372</v>
+      </c>
+      <c r="H8" t="s">
+        <v>352</v>
+      </c>
+      <c r="I8" t="s">
+        <v>373</v>
+      </c>
+      <c r="J8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C9" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" t="s">
+        <v>346</v>
+      </c>
+      <c r="E9" t="s">
+        <v>372</v>
+      </c>
+      <c r="H9" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" t="s">
+        <v>349</v>
+      </c>
+      <c r="J9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>375</v>
+      </c>
+      <c r="C10" t="s">
+        <v>376</v>
+      </c>
+      <c r="D10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C11" t="s">
+        <v>378</v>
+      </c>
+      <c r="D11" t="s">
+        <v>379</v>
+      </c>
+      <c r="N11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE622896-9186-4618-9113-EAE1C85306A1}">
+  <dimension ref="A1:AK4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I1" t="s">
+        <v>392</v>
+      </c>
+      <c r="J1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M1" t="s">
+        <v>396</v>
+      </c>
+      <c r="N1" t="s">
+        <v>397</v>
+      </c>
+      <c r="O1" t="s">
+        <v>398</v>
+      </c>
+      <c r="P1" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>400</v>
+      </c>
+      <c r="R1" t="s">
+        <v>401</v>
+      </c>
+      <c r="S1" t="s">
+        <v>402</v>
+      </c>
+      <c r="T1" t="s">
+        <v>403</v>
+      </c>
+      <c r="U1" t="s">
+        <v>404</v>
+      </c>
+      <c r="V1" t="s">
+        <v>405</v>
+      </c>
+      <c r="W1" t="s">
+        <v>406</v>
+      </c>
+      <c r="X1" t="s">
+        <v>407</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>408</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>410</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>413</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>414</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>415</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>418</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>419</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" t="s">
+        <v>426</v>
+      </c>
+      <c r="I2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J2" t="s">
+        <v>428</v>
+      </c>
+      <c r="K2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N2" t="s">
+        <v>430</v>
+      </c>
+      <c r="O2" t="s">
+        <v>431</v>
+      </c>
+      <c r="P2" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>271</v>
+      </c>
+      <c r="R2" t="s">
+        <v>271</v>
+      </c>
+      <c r="S2" t="s">
+        <v>433</v>
+      </c>
+      <c r="T2" t="s">
+        <v>433</v>
+      </c>
+      <c r="U2" t="s">
+        <v>434</v>
+      </c>
+      <c r="V2" t="s">
+        <v>435</v>
+      </c>
+      <c r="W2" t="s">
+        <v>436</v>
+      </c>
+      <c r="X2" t="s">
+        <v>437</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>438</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H3" t="s">
+        <v>442</v>
+      </c>
+      <c r="I3" t="s">
+        <v>427</v>
+      </c>
+      <c r="J3" t="s">
+        <v>428</v>
+      </c>
+      <c r="K3" t="s">
+        <v>429</v>
+      </c>
+      <c r="L3" t="s">
+        <v>137</v>
+      </c>
+      <c r="M3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N3" t="s">
+        <v>443</v>
+      </c>
+      <c r="O3" t="s">
+        <v>444</v>
+      </c>
+      <c r="P3" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>271</v>
+      </c>
+      <c r="R3" t="s">
+        <v>271</v>
+      </c>
+      <c r="S3" t="s">
+        <v>433</v>
+      </c>
+      <c r="T3" t="s">
+        <v>433</v>
+      </c>
+      <c r="U3" t="s">
+        <v>434</v>
+      </c>
+      <c r="V3" t="s">
+        <v>435</v>
+      </c>
+      <c r="W3" t="s">
+        <v>436</v>
+      </c>
+      <c r="X3" t="s">
+        <v>437</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>438</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F4" t="s">
+        <v>424</v>
+      </c>
+      <c r="G4" t="s">
+        <v>425</v>
+      </c>
+      <c r="H4" t="s">
+        <v>426</v>
+      </c>
+      <c r="I4" t="s">
+        <v>427</v>
+      </c>
+      <c r="J4" t="s">
+        <v>428</v>
+      </c>
+      <c r="K4" t="s">
+        <v>429</v>
+      </c>
+      <c r="L4" t="s">
+        <v>137</v>
+      </c>
+      <c r="M4" t="s">
+        <v>160</v>
+      </c>
+      <c r="N4" t="s">
+        <v>430</v>
+      </c>
+      <c r="O4" t="s">
+        <v>445</v>
+      </c>
+      <c r="P4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>140</v>
+      </c>
+      <c r="R4" t="s">
+        <v>140</v>
+      </c>
+      <c r="S4" t="s">
+        <v>433</v>
+      </c>
+      <c r="T4" t="s">
+        <v>433</v>
+      </c>
+      <c r="U4" t="s">
+        <v>434</v>
+      </c>
+      <c r="V4" t="s">
+        <v>435</v>
+      </c>
+      <c r="W4" t="s">
+        <v>436</v>
+      </c>
+      <c r="X4" t="s">
+        <v>437</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>438</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>433</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>434</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>435</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>436</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>437</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>438</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>427</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8B1889-F32E-450F-AC05-DE255B047530}">
+  <dimension ref="A1:AB22"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L1" t="s">
+        <v>451</v>
+      </c>
+      <c r="M1" t="s">
+        <v>452</v>
+      </c>
+      <c r="N1" t="s">
+        <v>453</v>
+      </c>
+      <c r="O1" t="s">
+        <v>454</v>
+      </c>
+      <c r="P1" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>456</v>
+      </c>
+      <c r="R1" t="s">
+        <v>457</v>
+      </c>
+      <c r="S1" t="s">
+        <v>458</v>
+      </c>
+      <c r="T1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U1" t="s">
+        <v>459</v>
+      </c>
+      <c r="V1" t="s">
+        <v>460</v>
+      </c>
+      <c r="W1" t="s">
+        <v>461</v>
+      </c>
+      <c r="X1" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>465</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I2" t="s">
+        <v>472</v>
+      </c>
+      <c r="J2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M2" t="s">
+        <v>474</v>
+      </c>
+      <c r="N2" t="s">
+        <v>475</v>
+      </c>
+      <c r="O2" t="s">
+        <v>476</v>
+      </c>
+      <c r="P2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>478</v>
+      </c>
+      <c r="R2" t="s">
+        <v>479</v>
+      </c>
+      <c r="S2" t="s">
+        <v>480</v>
+      </c>
+      <c r="T2" t="s">
+        <v>476</v>
+      </c>
+      <c r="U2" t="s">
+        <v>481</v>
+      </c>
+      <c r="V2" t="s">
+        <v>482</v>
+      </c>
+      <c r="W2" t="s">
+        <v>483</v>
+      </c>
+      <c r="X2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D3" t="s">
+        <v>486</v>
+      </c>
+      <c r="E3" t="s">
+        <v>470</v>
+      </c>
+      <c r="F3" t="s">
+        <v>471</v>
+      </c>
+      <c r="G3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I3" t="s">
+        <v>487</v>
+      </c>
+      <c r="J3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L3" t="s">
+        <v>488</v>
+      </c>
+      <c r="M3" t="s">
+        <v>474</v>
+      </c>
+      <c r="N3" t="s">
+        <v>475</v>
+      </c>
+      <c r="O3" t="s">
+        <v>489</v>
+      </c>
+      <c r="P3" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>490</v>
+      </c>
+      <c r="R3" t="s">
+        <v>491</v>
+      </c>
+      <c r="S3" t="s">
+        <v>492</v>
+      </c>
+      <c r="T3" t="s">
+        <v>489</v>
+      </c>
+      <c r="U3" t="s">
+        <v>481</v>
+      </c>
+      <c r="V3" t="s">
+        <v>482</v>
+      </c>
+      <c r="W3" t="s">
+        <v>483</v>
+      </c>
+      <c r="X3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E4" t="s">
+        <v>470</v>
+      </c>
+      <c r="F4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" t="s">
+        <v>352</v>
+      </c>
+      <c r="I4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" t="s">
+        <v>347</v>
+      </c>
+      <c r="L4" t="s">
+        <v>495</v>
+      </c>
+      <c r="M4" t="s">
+        <v>474</v>
+      </c>
+      <c r="N4" t="s">
+        <v>475</v>
+      </c>
+      <c r="O4" t="s">
+        <v>496</v>
+      </c>
+      <c r="P4" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>497</v>
+      </c>
+      <c r="R4" t="s">
+        <v>498</v>
+      </c>
+      <c r="S4" t="s">
+        <v>499</v>
+      </c>
+      <c r="T4" t="s">
+        <v>496</v>
+      </c>
+      <c r="U4" t="s">
+        <v>481</v>
+      </c>
+      <c r="V4" t="s">
+        <v>482</v>
+      </c>
+      <c r="W4" t="s">
+        <v>483</v>
+      </c>
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" t="s">
+        <v>500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>501</v>
+      </c>
+      <c r="E5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F5" t="s">
+        <v>471</v>
+      </c>
+      <c r="G5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H5" t="s">
+        <v>502</v>
+      </c>
+      <c r="I5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" t="s">
+        <v>503</v>
+      </c>
+      <c r="L5" t="s">
+        <v>504</v>
+      </c>
+      <c r="M5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O5" t="s">
+        <v>160</v>
+      </c>
+      <c r="P5" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>505</v>
+      </c>
+      <c r="R5" t="s">
+        <v>140</v>
+      </c>
+      <c r="S5" t="s">
+        <v>140</v>
+      </c>
+      <c r="T5" t="s">
+        <v>160</v>
+      </c>
+      <c r="U5" t="s">
+        <v>506</v>
+      </c>
+      <c r="V5" t="s">
+        <v>482</v>
+      </c>
+      <c r="W5" t="s">
+        <v>483</v>
+      </c>
+      <c r="X5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>505</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E6" t="s">
+        <v>470</v>
+      </c>
+      <c r="F6" t="s">
+        <v>471</v>
+      </c>
+      <c r="G6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" t="s">
+        <v>502</v>
+      </c>
+      <c r="I6" t="s">
+        <v>276</v>
+      </c>
+      <c r="J6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" t="s">
+        <v>347</v>
+      </c>
+      <c r="L6" t="s">
+        <v>509</v>
+      </c>
+      <c r="M6" t="s">
+        <v>510</v>
+      </c>
+      <c r="N6" t="s">
+        <v>511</v>
+      </c>
+      <c r="O6" t="s">
+        <v>160</v>
+      </c>
+      <c r="P6" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>512</v>
+      </c>
+      <c r="R6" t="s">
+        <v>513</v>
+      </c>
+      <c r="S6" t="s">
+        <v>514</v>
+      </c>
+      <c r="T6" t="s">
+        <v>160</v>
+      </c>
+      <c r="U6" t="s">
+        <v>515</v>
+      </c>
+      <c r="V6" t="s">
+        <v>482</v>
+      </c>
+      <c r="W6" t="s">
+        <v>483</v>
+      </c>
+      <c r="X6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D7" t="s">
+        <v>517</v>
+      </c>
+      <c r="E7" t="s">
+        <v>470</v>
+      </c>
+      <c r="F7" t="s">
+        <v>471</v>
+      </c>
+      <c r="G7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" t="s">
+        <v>502</v>
+      </c>
+      <c r="I7" t="s">
+        <v>276</v>
+      </c>
+      <c r="J7" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" t="s">
+        <v>347</v>
+      </c>
+      <c r="L7" t="s">
+        <v>509</v>
+      </c>
+      <c r="M7" t="s">
+        <v>510</v>
+      </c>
+      <c r="N7" t="s">
+        <v>511</v>
+      </c>
+      <c r="O7" t="s">
+        <v>160</v>
+      </c>
+      <c r="P7" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>512</v>
+      </c>
+      <c r="R7" t="s">
+        <v>513</v>
+      </c>
+      <c r="S7" t="s">
+        <v>514</v>
+      </c>
+      <c r="T7" t="s">
+        <v>160</v>
+      </c>
+      <c r="U7" t="s">
+        <v>481</v>
+      </c>
+      <c r="V7" t="s">
+        <v>482</v>
+      </c>
+      <c r="W7" t="s">
+        <v>483</v>
+      </c>
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C8" t="s">
+        <v>518</v>
+      </c>
+      <c r="D8" t="s">
+        <v>508</v>
+      </c>
+      <c r="E8" t="s">
+        <v>470</v>
+      </c>
+      <c r="F8" t="s">
+        <v>471</v>
+      </c>
+      <c r="G8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" t="s">
+        <v>519</v>
+      </c>
+      <c r="I8" t="s">
+        <v>152</v>
+      </c>
+      <c r="J8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L8" t="s">
+        <v>520</v>
+      </c>
+      <c r="M8" t="s">
+        <v>474</v>
+      </c>
+      <c r="N8" t="s">
+        <v>521</v>
+      </c>
+      <c r="O8" t="s">
+        <v>160</v>
+      </c>
+      <c r="P8" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>522</v>
+      </c>
+      <c r="R8" t="s">
+        <v>523</v>
+      </c>
+      <c r="S8" t="s">
+        <v>514</v>
+      </c>
+      <c r="T8" t="s">
+        <v>160</v>
+      </c>
+      <c r="U8" t="s">
+        <v>524</v>
+      </c>
+      <c r="V8" t="s">
+        <v>482</v>
+      </c>
+      <c r="W8" t="s">
+        <v>483</v>
+      </c>
+      <c r="X8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C9" t="s">
+        <v>525</v>
+      </c>
+      <c r="D9" t="s">
+        <v>508</v>
+      </c>
+      <c r="E9" t="s">
+        <v>470</v>
+      </c>
+      <c r="F9" t="s">
+        <v>471</v>
+      </c>
+      <c r="G9" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" t="s">
+        <v>502</v>
+      </c>
+      <c r="I9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" t="s">
+        <v>347</v>
+      </c>
+      <c r="L9" t="s">
+        <v>526</v>
+      </c>
+      <c r="M9" t="s">
+        <v>527</v>
+      </c>
+      <c r="N9" t="s">
+        <v>528</v>
+      </c>
+      <c r="O9" t="s">
+        <v>160</v>
+      </c>
+      <c r="P9" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>529</v>
+      </c>
+      <c r="R9" t="s">
+        <v>513</v>
+      </c>
+      <c r="S9" t="s">
+        <v>514</v>
+      </c>
+      <c r="T9" t="s">
+        <v>160</v>
+      </c>
+      <c r="U9" t="s">
+        <v>515</v>
+      </c>
+      <c r="V9" t="s">
+        <v>482</v>
+      </c>
+      <c r="W9" t="s">
+        <v>483</v>
+      </c>
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>467</v>
+      </c>
+      <c r="C10" t="s">
+        <v>516</v>
+      </c>
+      <c r="D10" t="s">
+        <v>517</v>
+      </c>
+      <c r="E10" t="s">
+        <v>470</v>
+      </c>
+      <c r="F10" t="s">
+        <v>471</v>
+      </c>
+      <c r="G10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H10" t="s">
+        <v>502</v>
+      </c>
+      <c r="I10" t="s">
+        <v>276</v>
+      </c>
+      <c r="J10" t="s">
+        <v>156</v>
+      </c>
+      <c r="K10" t="s">
+        <v>347</v>
+      </c>
+      <c r="L10" t="s">
+        <v>509</v>
+      </c>
+      <c r="M10" t="s">
+        <v>510</v>
+      </c>
+      <c r="N10" t="s">
+        <v>511</v>
+      </c>
+      <c r="O10" t="s">
+        <v>160</v>
+      </c>
+      <c r="P10" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>512</v>
+      </c>
+      <c r="R10" t="s">
+        <v>513</v>
+      </c>
+      <c r="S10" t="s">
+        <v>514</v>
+      </c>
+      <c r="T10" t="s">
+        <v>160</v>
+      </c>
+      <c r="U10" t="s">
+        <v>481</v>
+      </c>
+      <c r="V10" t="s">
+        <v>482</v>
+      </c>
+      <c r="W10" t="s">
+        <v>483</v>
+      </c>
+      <c r="X10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>467</v>
+      </c>
+      <c r="C11" t="s">
+        <v>530</v>
+      </c>
+      <c r="D11" t="s">
+        <v>508</v>
+      </c>
+      <c r="E11" t="s">
+        <v>470</v>
+      </c>
+      <c r="F11" t="s">
+        <v>471</v>
+      </c>
+      <c r="G11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" t="s">
+        <v>519</v>
+      </c>
+      <c r="I11" t="s">
+        <v>531</v>
+      </c>
+      <c r="J11" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" t="s">
+        <v>347</v>
+      </c>
+      <c r="L11" t="s">
+        <v>532</v>
+      </c>
+      <c r="M11" t="s">
+        <v>527</v>
+      </c>
+      <c r="N11" t="s">
+        <v>533</v>
+      </c>
+      <c r="O11" t="s">
+        <v>160</v>
+      </c>
+      <c r="P11" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>534</v>
+      </c>
+      <c r="R11" t="s">
+        <v>535</v>
+      </c>
+      <c r="S11" t="s">
+        <v>536</v>
+      </c>
+      <c r="T11" t="s">
+        <v>537</v>
+      </c>
+      <c r="U11" t="s">
+        <v>481</v>
+      </c>
+      <c r="V11" t="s">
+        <v>482</v>
+      </c>
+      <c r="W11" t="s">
+        <v>483</v>
+      </c>
+      <c r="X11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D12" t="s">
+        <v>538</v>
+      </c>
+      <c r="E12" t="s">
+        <v>470</v>
+      </c>
+      <c r="F12" t="s">
+        <v>471</v>
+      </c>
+      <c r="G12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" t="s">
+        <v>349</v>
+      </c>
+      <c r="I12" t="s">
+        <v>276</v>
+      </c>
+      <c r="J12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" t="s">
+        <v>347</v>
+      </c>
+      <c r="L12" t="s">
+        <v>526</v>
+      </c>
+      <c r="M12" t="s">
+        <v>527</v>
+      </c>
+      <c r="N12" t="s">
+        <v>528</v>
+      </c>
+      <c r="O12" t="s">
+        <v>160</v>
+      </c>
+      <c r="P12" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>529</v>
+      </c>
+      <c r="R12" t="s">
+        <v>513</v>
+      </c>
+      <c r="S12" t="s">
+        <v>514</v>
+      </c>
+      <c r="T12" t="s">
+        <v>160</v>
+      </c>
+      <c r="U12" t="s">
+        <v>515</v>
+      </c>
+      <c r="V12" t="s">
+        <v>482</v>
+      </c>
+      <c r="W12" t="s">
+        <v>483</v>
+      </c>
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>467</v>
+      </c>
+      <c r="C13" t="s">
+        <v>539</v>
+      </c>
+      <c r="D13" t="s">
+        <v>540</v>
+      </c>
+      <c r="E13" t="s">
+        <v>470</v>
+      </c>
+      <c r="F13" t="s">
+        <v>471</v>
+      </c>
+      <c r="G13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" t="s">
+        <v>519</v>
+      </c>
+      <c r="I13" t="s">
+        <v>152</v>
+      </c>
+      <c r="J13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K13" t="s">
+        <v>347</v>
+      </c>
+      <c r="L13" t="s">
+        <v>520</v>
+      </c>
+      <c r="M13" t="s">
+        <v>474</v>
+      </c>
+      <c r="N13" t="s">
+        <v>521</v>
+      </c>
+      <c r="O13" t="s">
+        <v>160</v>
+      </c>
+      <c r="P13" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>512</v>
+      </c>
+      <c r="R13" t="s">
+        <v>513</v>
+      </c>
+      <c r="S13" t="s">
+        <v>514</v>
+      </c>
+      <c r="T13" t="s">
+        <v>160</v>
+      </c>
+      <c r="U13" t="s">
+        <v>541</v>
+      </c>
+      <c r="V13" t="s">
+        <v>482</v>
+      </c>
+      <c r="W13" t="s">
+        <v>483</v>
+      </c>
+      <c r="X13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>467</v>
+      </c>
+      <c r="C14" t="s">
+        <v>542</v>
+      </c>
+      <c r="D14" t="s">
+        <v>543</v>
+      </c>
+      <c r="E14" t="s">
+        <v>470</v>
+      </c>
+      <c r="F14" t="s">
+        <v>471</v>
+      </c>
+      <c r="G14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" t="s">
+        <v>519</v>
+      </c>
+      <c r="I14" t="s">
+        <v>276</v>
+      </c>
+      <c r="J14" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" t="s">
+        <v>347</v>
+      </c>
+      <c r="L14" t="s">
+        <v>520</v>
+      </c>
+      <c r="M14" t="s">
+        <v>474</v>
+      </c>
+      <c r="N14" t="s">
+        <v>521</v>
+      </c>
+      <c r="O14" t="s">
+        <v>544</v>
+      </c>
+      <c r="P14" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>545</v>
+      </c>
+      <c r="R14" t="s">
+        <v>523</v>
+      </c>
+      <c r="S14" t="s">
+        <v>514</v>
+      </c>
+      <c r="T14" t="s">
+        <v>544</v>
+      </c>
+      <c r="U14" t="s">
+        <v>546</v>
+      </c>
+      <c r="V14" t="s">
+        <v>482</v>
+      </c>
+      <c r="W14" t="s">
+        <v>483</v>
+      </c>
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" t="s">
+        <v>547</v>
+      </c>
+      <c r="D15" t="s">
+        <v>548</v>
+      </c>
+      <c r="E15" t="s">
+        <v>470</v>
+      </c>
+      <c r="F15" t="s">
+        <v>471</v>
+      </c>
+      <c r="G15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" t="s">
+        <v>349</v>
+      </c>
+      <c r="I15" t="s">
+        <v>276</v>
+      </c>
+      <c r="J15" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L15" t="s">
+        <v>520</v>
+      </c>
+      <c r="M15" t="s">
+        <v>474</v>
+      </c>
+      <c r="N15" t="s">
+        <v>521</v>
+      </c>
+      <c r="O15" t="s">
+        <v>544</v>
+      </c>
+      <c r="P15" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>529</v>
+      </c>
+      <c r="R15" t="s">
+        <v>513</v>
+      </c>
+      <c r="S15" t="s">
+        <v>514</v>
+      </c>
+      <c r="T15" t="s">
+        <v>160</v>
+      </c>
+      <c r="U15" t="s">
+        <v>515</v>
+      </c>
+      <c r="V15" t="s">
+        <v>482</v>
+      </c>
+      <c r="W15" t="s">
+        <v>483</v>
+      </c>
+      <c r="X15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>467</v>
+      </c>
+      <c r="C16" t="s">
+        <v>549</v>
+      </c>
+      <c r="D16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E16" t="s">
+        <v>470</v>
+      </c>
+      <c r="F16" t="s">
+        <v>471</v>
+      </c>
+      <c r="G16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H16" t="s">
+        <v>349</v>
+      </c>
+      <c r="I16" t="s">
+        <v>152</v>
+      </c>
+      <c r="J16" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" t="s">
+        <v>347</v>
+      </c>
+      <c r="L16" t="s">
+        <v>504</v>
+      </c>
+      <c r="M16" t="s">
+        <v>474</v>
+      </c>
+      <c r="N16" t="s">
+        <v>474</v>
+      </c>
+      <c r="O16" t="s">
+        <v>160</v>
+      </c>
+      <c r="P16" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>512</v>
+      </c>
+      <c r="R16" t="s">
+        <v>513</v>
+      </c>
+      <c r="S16" t="s">
+        <v>514</v>
+      </c>
+      <c r="T16" t="s">
+        <v>160</v>
+      </c>
+      <c r="U16" t="s">
+        <v>541</v>
+      </c>
+      <c r="V16" t="s">
+        <v>482</v>
+      </c>
+      <c r="W16" t="s">
+        <v>483</v>
+      </c>
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>467</v>
+      </c>
+      <c r="C17" t="s">
+        <v>551</v>
+      </c>
+      <c r="D17" t="s">
+        <v>552</v>
+      </c>
+      <c r="E17" t="s">
+        <v>470</v>
+      </c>
+      <c r="F17" t="s">
+        <v>471</v>
+      </c>
+      <c r="G17" t="s">
+        <v>151</v>
+      </c>
+      <c r="H17" t="s">
+        <v>349</v>
+      </c>
+      <c r="I17" t="s">
+        <v>276</v>
+      </c>
+      <c r="J17" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17" t="s">
+        <v>347</v>
+      </c>
+      <c r="L17" t="s">
+        <v>520</v>
+      </c>
+      <c r="M17" t="s">
+        <v>474</v>
+      </c>
+      <c r="N17" t="s">
+        <v>521</v>
+      </c>
+      <c r="O17" t="s">
+        <v>544</v>
+      </c>
+      <c r="P17" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>545</v>
+      </c>
+      <c r="R17" t="s">
+        <v>523</v>
+      </c>
+      <c r="S17" t="s">
+        <v>514</v>
+      </c>
+      <c r="T17" t="s">
+        <v>160</v>
+      </c>
+      <c r="U17" t="s">
+        <v>546</v>
+      </c>
+      <c r="V17" t="s">
+        <v>482</v>
+      </c>
+      <c r="W17" t="s">
+        <v>483</v>
+      </c>
+      <c r="X17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" t="s">
+        <v>507</v>
+      </c>
+      <c r="D18" t="s">
+        <v>508</v>
+      </c>
+      <c r="E18" t="s">
+        <v>470</v>
+      </c>
+      <c r="F18" t="s">
+        <v>471</v>
+      </c>
+      <c r="G18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H18" t="s">
+        <v>553</v>
+      </c>
+      <c r="I18" t="s">
+        <v>276</v>
+      </c>
+      <c r="J18" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" t="s">
+        <v>347</v>
+      </c>
+      <c r="L18" t="s">
+        <v>509</v>
+      </c>
+      <c r="M18" t="s">
+        <v>510</v>
+      </c>
+      <c r="N18" t="s">
+        <v>511</v>
+      </c>
+      <c r="O18" t="s">
+        <v>160</v>
+      </c>
+      <c r="P18" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>512</v>
+      </c>
+      <c r="R18" t="s">
+        <v>513</v>
+      </c>
+      <c r="S18" t="s">
+        <v>514</v>
+      </c>
+      <c r="T18" t="s">
+        <v>160</v>
+      </c>
+      <c r="U18" t="s">
+        <v>515</v>
+      </c>
+      <c r="V18" t="s">
+        <v>482</v>
+      </c>
+      <c r="W18" t="s">
+        <v>483</v>
+      </c>
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>467</v>
+      </c>
+      <c r="C19" t="s">
+        <v>554</v>
+      </c>
+      <c r="D19" t="s">
+        <v>494</v>
+      </c>
+      <c r="E19" t="s">
+        <v>470</v>
+      </c>
+      <c r="F19" t="s">
+        <v>471</v>
+      </c>
+      <c r="G19" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" t="s">
+        <v>349</v>
+      </c>
+      <c r="I19" t="s">
+        <v>277</v>
+      </c>
+      <c r="J19" t="s">
+        <v>114</v>
+      </c>
+      <c r="K19" t="s">
+        <v>347</v>
+      </c>
+      <c r="L19" t="s">
+        <v>495</v>
+      </c>
+      <c r="M19" t="s">
+        <v>474</v>
+      </c>
+      <c r="N19" t="s">
+        <v>475</v>
+      </c>
+      <c r="O19" t="s">
+        <v>496</v>
+      </c>
+      <c r="P19" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>497</v>
+      </c>
+      <c r="R19" t="s">
+        <v>498</v>
+      </c>
+      <c r="S19" t="s">
+        <v>499</v>
+      </c>
+      <c r="T19" t="s">
+        <v>496</v>
+      </c>
+      <c r="U19" t="s">
+        <v>481</v>
+      </c>
+      <c r="V19" t="s">
+        <v>482</v>
+      </c>
+      <c r="W19" t="s">
+        <v>483</v>
+      </c>
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>467</v>
+      </c>
+      <c r="C20" t="s">
+        <v>555</v>
+      </c>
+      <c r="D20" t="s">
+        <v>556</v>
+      </c>
+      <c r="E20" t="s">
+        <v>470</v>
+      </c>
+      <c r="F20" t="s">
+        <v>471</v>
+      </c>
+      <c r="G20" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" t="s">
+        <v>349</v>
+      </c>
+      <c r="I20" t="s">
+        <v>276</v>
+      </c>
+      <c r="J20" t="s">
+        <v>114</v>
+      </c>
+      <c r="K20" t="s">
+        <v>347</v>
+      </c>
+      <c r="L20" t="s">
+        <v>509</v>
+      </c>
+      <c r="M20" t="s">
+        <v>510</v>
+      </c>
+      <c r="N20" t="s">
+        <v>511</v>
+      </c>
+      <c r="O20" t="s">
+        <v>544</v>
+      </c>
+      <c r="P20" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>505</v>
+      </c>
+      <c r="R20" t="s">
+        <v>557</v>
+      </c>
+      <c r="S20" t="s">
+        <v>514</v>
+      </c>
+      <c r="T20" t="s">
+        <v>544</v>
+      </c>
+      <c r="U20" t="s">
+        <v>481</v>
+      </c>
+      <c r="V20" t="s">
+        <v>482</v>
+      </c>
+      <c r="W20" t="s">
+        <v>483</v>
+      </c>
+      <c r="X20" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>467</v>
+      </c>
+      <c r="C21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D21" t="s">
+        <v>559</v>
+      </c>
+      <c r="E21" t="s">
+        <v>470</v>
+      </c>
+      <c r="F21" t="s">
+        <v>471</v>
+      </c>
+      <c r="G21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I21" t="s">
+        <v>531</v>
+      </c>
+      <c r="J21" t="s">
+        <v>114</v>
+      </c>
+      <c r="K21" t="s">
+        <v>347</v>
+      </c>
+      <c r="L21" t="s">
+        <v>532</v>
+      </c>
+      <c r="M21" t="s">
+        <v>527</v>
+      </c>
+      <c r="N21" t="s">
+        <v>533</v>
+      </c>
+      <c r="O21" t="s">
+        <v>160</v>
+      </c>
+      <c r="P21" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>534</v>
+      </c>
+      <c r="R21" t="s">
+        <v>535</v>
+      </c>
+      <c r="S21" t="s">
+        <v>536</v>
+      </c>
+      <c r="T21" t="s">
+        <v>537</v>
+      </c>
+      <c r="U21" t="s">
+        <v>481</v>
+      </c>
+      <c r="V21" t="s">
+        <v>482</v>
+      </c>
+      <c r="W21" t="s">
+        <v>483</v>
+      </c>
+      <c r="X21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C22" t="s">
+        <v>500</v>
+      </c>
+      <c r="D22" t="s">
+        <v>501</v>
+      </c>
+      <c r="E22" t="s">
+        <v>470</v>
+      </c>
+      <c r="F22" t="s">
+        <v>471</v>
+      </c>
+      <c r="G22" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" t="s">
+        <v>353</v>
+      </c>
+      <c r="I22" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22" t="s">
+        <v>114</v>
+      </c>
+      <c r="K22" t="s">
+        <v>503</v>
+      </c>
+      <c r="L22" t="s">
+        <v>504</v>
+      </c>
+      <c r="M22" t="s">
+        <v>140</v>
+      </c>
+      <c r="N22" t="s">
+        <v>140</v>
+      </c>
+      <c r="O22" t="s">
+        <v>160</v>
+      </c>
+      <c r="P22" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>505</v>
+      </c>
+      <c r="R22" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" t="s">
+        <v>140</v>
+      </c>
+      <c r="T22" t="s">
+        <v>160</v>
+      </c>
+      <c r="U22" t="s">
+        <v>506</v>
+      </c>
+      <c r="V22" t="s">
+        <v>482</v>
+      </c>
+      <c r="W22" t="s">
+        <v>483</v>
+      </c>
+      <c r="X22" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>505</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9395AF-F3CF-4269-9F63-96748F1DA265}">
+  <dimension ref="A1:AV2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>560</v>
+      </c>
+      <c r="L1" t="s">
+        <v>561</v>
+      </c>
+      <c r="M1" t="s">
+        <v>562</v>
+      </c>
+      <c r="N1" t="s">
+        <v>563</v>
+      </c>
+      <c r="O1" t="s">
+        <v>564</v>
+      </c>
+      <c r="P1" t="s">
+        <v>565</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>269</v>
+      </c>
+      <c r="R1" t="s">
+        <v>566</v>
+      </c>
+      <c r="S1" t="s">
+        <v>567</v>
+      </c>
+      <c r="T1" t="s">
+        <v>568</v>
+      </c>
+      <c r="U1" t="s">
+        <v>569</v>
+      </c>
+      <c r="V1" t="s">
+        <v>570</v>
+      </c>
+      <c r="W1" t="s">
+        <v>571</v>
+      </c>
+      <c r="X1" t="s">
+        <v>572</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>573</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>574</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>575</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>576</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>577</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>578</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>579</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>580</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>581</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>582</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>583</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>584</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>586</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>587</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>588</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>590</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>591</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>300</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>593</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>594</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" t="s">
+        <v>600</v>
+      </c>
+      <c r="L2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M2" t="s">
+        <v>601</v>
+      </c>
+      <c r="N2" t="s">
+        <v>323</v>
+      </c>
+      <c r="O2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P2" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>603</v>
+      </c>
+      <c r="R2" t="s">
+        <v>604</v>
+      </c>
+      <c r="S2" t="s">
+        <v>605</v>
+      </c>
+      <c r="T2" t="s">
+        <v>606</v>
+      </c>
+      <c r="U2" t="s">
+        <v>607</v>
+      </c>
+      <c r="V2" t="s">
+        <v>608</v>
+      </c>
+      <c r="W2" t="s">
+        <v>609</v>
+      </c>
+      <c r="X2" t="s">
+        <v>610</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>611</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>612</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>614</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>616</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>617</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>618</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>619</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>620</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>621</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>622</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>623</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>624</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>625</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>626</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>315</v>
+      </c>
+      <c r="AR2">
+        <v>4100002353</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>627</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>628</v>
+      </c>
+      <c r="AU2">
+        <v>9200000637</v>
+      </c>
+      <c r="AV2">
+        <v>9200000638</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.08203125" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>197</v>
       </c>
@@ -2063,7 +6861,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -2092,7 +6890,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>206</v>
       </c>
@@ -2121,7 +6919,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>206</v>
       </c>
@@ -2150,7 +6948,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>212</v>
       </c>
@@ -2177,12 +6975,2723 @@
       </c>
       <c r="I5" t="s">
         <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G13" t="s">
+        <v>227</v>
+      </c>
+      <c r="H13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" t="s">
+        <v>191</v>
+      </c>
+      <c r="G14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" t="s">
+        <v>191</v>
+      </c>
+      <c r="G15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" t="s">
+        <v>191</v>
+      </c>
+      <c r="G16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E19" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" t="s">
+        <v>219</v>
+      </c>
+      <c r="H19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" t="s">
+        <v>219</v>
+      </c>
+      <c r="H20" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>251</v>
+      </c>
+      <c r="D21" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>151</v>
+      </c>
+      <c r="G21" t="s">
+        <v>253</v>
+      </c>
+      <c r="H21" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>255</v>
+      </c>
+      <c r="D22" t="s">
+        <v>252</v>
+      </c>
+      <c r="E22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" t="s">
+        <v>252</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" t="s">
+        <v>252</v>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" t="s">
+        <v>260</v>
+      </c>
+      <c r="H25" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G26" t="s">
+        <v>262</v>
+      </c>
+      <c r="H26" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>263</v>
+      </c>
+      <c r="D27" t="s">
+        <v>252</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" t="s">
+        <v>140</v>
+      </c>
+      <c r="I27" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D28" t="s">
+        <v>252</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>151</v>
+      </c>
+      <c r="G28" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" t="s">
+        <v>140</v>
+      </c>
+      <c r="I28" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>629</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>630</v>
+      </c>
+      <c r="D29" t="s">
+        <v>631</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" t="s">
+        <v>140</v>
+      </c>
+      <c r="I29" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>467</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>632</v>
+      </c>
+      <c r="D30" t="s">
+        <v>470</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" t="s">
+        <v>140</v>
+      </c>
+      <c r="I30" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>596</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>633</v>
+      </c>
+      <c r="D31" t="s">
+        <v>634</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" t="s">
+        <v>140</v>
+      </c>
+      <c r="H31" t="s">
+        <v>140</v>
+      </c>
+      <c r="I31" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>596</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>635</v>
+      </c>
+      <c r="D32" t="s">
+        <v>634</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>596</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>636</v>
+      </c>
+      <c r="D33" t="s">
+        <v>634</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" t="s">
+        <v>140</v>
+      </c>
+      <c r="H33" t="s">
+        <v>140</v>
+      </c>
+      <c r="I33" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>596</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>637</v>
+      </c>
+      <c r="D34" t="s">
+        <v>634</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>596</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>638</v>
+      </c>
+      <c r="D35" t="s">
+        <v>634</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>151</v>
+      </c>
+      <c r="G35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" t="s">
+        <v>140</v>
+      </c>
+      <c r="I35" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>596</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>639</v>
+      </c>
+      <c r="D36" t="s">
+        <v>634</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" t="s">
+        <v>140</v>
+      </c>
+      <c r="H36" t="s">
+        <v>140</v>
+      </c>
+      <c r="I36" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>596</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>640</v>
+      </c>
+      <c r="D37" t="s">
+        <v>634</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>151</v>
+      </c>
+      <c r="G37" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" t="s">
+        <v>140</v>
+      </c>
+      <c r="I37" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>596</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>641</v>
+      </c>
+      <c r="D38" t="s">
+        <v>634</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" t="s">
+        <v>140</v>
+      </c>
+      <c r="I38" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>596</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>642</v>
+      </c>
+      <c r="D39" t="s">
+        <v>634</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" t="s">
+        <v>140</v>
+      </c>
+      <c r="I39" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>596</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>643</v>
+      </c>
+      <c r="D40" t="s">
+        <v>634</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>191</v>
+      </c>
+      <c r="G40" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" t="s">
+        <v>140</v>
+      </c>
+      <c r="I40" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>596</v>
+      </c>
+      <c r="B41">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>644</v>
+      </c>
+      <c r="D41" t="s">
+        <v>634</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41" t="s">
+        <v>140</v>
+      </c>
+      <c r="H41" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>596</v>
+      </c>
+      <c r="B42">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>645</v>
+      </c>
+      <c r="D42" t="s">
+        <v>634</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>191</v>
+      </c>
+      <c r="G42" t="s">
+        <v>140</v>
+      </c>
+      <c r="H42" t="s">
+        <v>140</v>
+      </c>
+      <c r="I42" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>596</v>
+      </c>
+      <c r="B43">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>646</v>
+      </c>
+      <c r="D43" t="s">
+        <v>634</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" t="s">
+        <v>140</v>
+      </c>
+      <c r="H43" t="s">
+        <v>140</v>
+      </c>
+      <c r="I43" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>596</v>
+      </c>
+      <c r="B44">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>647</v>
+      </c>
+      <c r="D44" t="s">
+        <v>634</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" t="s">
+        <v>596</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I28" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G5" t="s">
+        <v>272</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" t="s">
+        <v>277</v>
+      </c>
+      <c r="D13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" t="s">
+        <v>140</v>
+      </c>
+      <c r="F14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" t="s">
+        <v>276</v>
+      </c>
+      <c r="D21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" t="s">
+        <v>140</v>
+      </c>
+      <c r="H21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" t="s">
+        <v>277</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>283</v>
+      </c>
+      <c r="C23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>283</v>
+      </c>
+      <c r="C24" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>283</v>
+      </c>
+      <c r="C25" t="s">
+        <v>277</v>
+      </c>
+      <c r="D25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>284</v>
+      </c>
+      <c r="C26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>284</v>
+      </c>
+      <c r="C28" t="s">
+        <v>277</v>
+      </c>
+      <c r="D28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>285</v>
+      </c>
+      <c r="C29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C31" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" t="s">
+        <v>140</v>
+      </c>
+      <c r="H31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C32" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" t="s">
+        <v>140</v>
+      </c>
+      <c r="H33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>286</v>
+      </c>
+      <c r="C34" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>287</v>
+      </c>
+      <c r="C35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>287</v>
+      </c>
+      <c r="C36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" t="s">
+        <v>140</v>
+      </c>
+      <c r="H36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" t="s">
+        <v>277</v>
+      </c>
+      <c r="D37" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" t="s">
+        <v>140</v>
+      </c>
+      <c r="G37" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>288</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F38" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>288</v>
+      </c>
+      <c r="C39" t="s">
+        <v>276</v>
+      </c>
+      <c r="D39" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" t="s">
+        <v>140</v>
+      </c>
+      <c r="F39" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" t="s">
+        <v>140</v>
+      </c>
+      <c r="G40" t="s">
+        <v>140</v>
+      </c>
+      <c r="H40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>289</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" t="s">
+        <v>140</v>
+      </c>
+      <c r="H41" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>289</v>
+      </c>
+      <c r="C42" t="s">
+        <v>276</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>140</v>
+      </c>
+      <c r="F42" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" t="s">
+        <v>140</v>
+      </c>
+      <c r="H42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>289</v>
+      </c>
+      <c r="C43" t="s">
+        <v>277</v>
+      </c>
+      <c r="D43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" t="s">
+        <v>140</v>
+      </c>
+      <c r="H43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>290</v>
+      </c>
+      <c r="C44" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" t="s">
+        <v>140</v>
+      </c>
+      <c r="F44" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>290</v>
+      </c>
+      <c r="C45" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" t="s">
+        <v>140</v>
+      </c>
+      <c r="E45" t="s">
+        <v>140</v>
+      </c>
+      <c r="F45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45" t="s">
+        <v>140</v>
+      </c>
+      <c r="H45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>290</v>
+      </c>
+      <c r="C46" t="s">
+        <v>277</v>
+      </c>
+      <c r="D46" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" t="s">
+        <v>140</v>
+      </c>
+      <c r="H46" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H46" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" t="s">
+        <v>272</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H8" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:D4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/test-data.xlsx
+++ b/data/test-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audtejas\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sinvisha11\Downloads\Clarien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F025147-75BA-4205-9736-C20A584DAD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3670A2B-CCB4-4DD7-A040-309AE38274A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRM" sheetId="1" r:id="rId1"/>
@@ -21,23 +21,24 @@
     <sheet name="SavingsAccountData" sheetId="3" r:id="rId6"/>
     <sheet name="CurrentAccountData" sheetId="4" r:id="rId7"/>
     <sheet name="SavingsAccountModifyData" sheetId="5" r:id="rId8"/>
-    <sheet name="SavingsAccountModifyVerifyData" sheetId="6" r:id="rId9"/>
-    <sheet name="SavingsAccountRelatedPartyData" sheetId="7" r:id="rId10"/>
-    <sheet name="SavingsAccountDelRelPartyData" sheetId="8" r:id="rId11"/>
-    <sheet name="SavingsAccountDelRelPartyVerify" sheetId="9" r:id="rId12"/>
-    <sheet name="SavingsAccountFreezeData" sheetId="10" r:id="rId13"/>
-    <sheet name="SavingsAccountUnfreezeData" sheetId="11" r:id="rId14"/>
-    <sheet name="SavingsAccountFreezeVerifyData" sheetId="12" r:id="rId15"/>
-    <sheet name="CurrentAccountModifyData" sheetId="13" r:id="rId16"/>
-    <sheet name="CurrentAccountModifyVerifyData" sheetId="14" r:id="rId17"/>
-    <sheet name="TransferMaintenanceData" sheetId="15" r:id="rId18"/>
+    <sheet name="topup_deposits" sheetId="19" r:id="rId9"/>
+    <sheet name="SavingsAccountModifyVerifyData" sheetId="6" r:id="rId10"/>
+    <sheet name="SavingsAccountRelatedPartyData" sheetId="7" r:id="rId11"/>
+    <sheet name="SavingsAccountDelRelPartyData" sheetId="8" r:id="rId12"/>
+    <sheet name="SavingsAccountDelRelPartyVerify" sheetId="9" r:id="rId13"/>
+    <sheet name="SavingsAccountFreezeData" sheetId="10" r:id="rId14"/>
+    <sheet name="SavingsAccountUnfreezeData" sheetId="11" r:id="rId15"/>
+    <sheet name="SavingsAccountFreezeVerifyData" sheetId="12" r:id="rId16"/>
+    <sheet name="CurrentAccountModifyData" sheetId="13" r:id="rId17"/>
+    <sheet name="CurrentAccountModifyVerifyData" sheetId="14" r:id="rId18"/>
+    <sheet name="TransferMaintenanceData" sheetId="15" r:id="rId19"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="686">
   <si>
     <t>instance</t>
   </si>
@@ -1981,6 +1982,120 @@
   </si>
   <si>
     <t>tests/Finacle/Termdeposits/termdepositssphtditci.spec.ts</t>
+  </si>
+  <si>
+    <t>initialDepositAmt</t>
+  </si>
+  <si>
+    <t>instalmentAmt</t>
+  </si>
+  <si>
+    <t>repaymentAcctId</t>
+  </si>
+  <si>
+    <t>nomination</t>
+  </si>
+  <si>
+    <t>statementFrequency</t>
+  </si>
+  <si>
+    <t>statementWeek</t>
+  </si>
+  <si>
+    <t>statementDay</t>
+  </si>
+  <si>
+    <t>statementNextDay</t>
+  </si>
+  <si>
+    <t>spTransferScreenCode</t>
+  </si>
+  <si>
+    <t>spTransferCreditAccount</t>
+  </si>
+  <si>
+    <t>spTransferDebitAccount</t>
+  </si>
+  <si>
+    <t>spTransferAmount</t>
+  </si>
+  <si>
+    <t>spTransferInstallmentType</t>
+  </si>
+  <si>
+    <t>modificationTestLabel</t>
+  </si>
+  <si>
+    <t>topupdeposit</t>
+  </si>
+  <si>
+    <t>Top-up Deposit - consolidated data</t>
+  </si>
+  <si>
+    <t>topUpDepositData</t>
+  </si>
+  <si>
+    <t>HOAACTU</t>
+  </si>
+  <si>
+    <t>SVRPL</t>
+  </si>
+  <si>
+    <t>["ACCCO","ACCPL","SVRCO","SVRPL"]</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>7500001511</t>
+  </si>
+  <si>
+    <t>Yearly</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Next Day</t>
+  </si>
+  <si>
+    <t>Email Only</t>
+  </si>
+  <si>
+    <t>{"create":"HOAACTU","modify":"HOAACMTU","verify":"HOAACVTU","partialClosure":"HCAACTD","partialClosureVerify":"HCAACVTD","prematureClosure":"HCAACTD","prematureClosureVerify":"HCAACVTD","renewal":"HTDREN","renewalVerify":"HTDREN"}</t>
+  </si>
+  <si>
+    <t>9300000123</t>
+  </si>
+  <si>
+    <t>9300000131</t>
+  </si>
+  <si>
+    <t>9200000632</t>
+  </si>
+  <si>
+    <t>4100058365</t>
+  </si>
+  <si>
+    <t>HTUTM</t>
+  </si>
+  <si>
+    <t>500USD2297007</t>
+  </si>
+  <si>
+    <t>Normal Installment</t>
+  </si>
+  <si>
+    <t>HOAACTU - create top-up deposit account</t>
+  </si>
+  <si>
+    <t>HOAACMTU - modify top-up deposit account</t>
+  </si>
+  <si>
+    <t>HOAACMTU - add related party details to top-up deposit account</t>
   </si>
 </sst>
 </file>
@@ -3345,6 +3460,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:D4" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3417,7 +3601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3442,41 +3626,6 @@
       </c>
       <c r="C2" t="s">
         <v>319</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C2" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3488,6 +3637,41 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3534,7 +3718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3559,41 +3743,6 @@
       </c>
       <c r="C2" t="s">
         <v>327</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C2" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -3605,6 +3754,41 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3697,7 +3881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3802,7 +3986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -9628,70 +9812,291 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2093496C-432F-472F-AA6D-681FBD70FEEA}">
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="C1" t="s">
-        <v>305</v>
+        <v>446</v>
       </c>
       <c r="D1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>560</v>
+      </c>
+      <c r="L1" t="s">
+        <v>265</v>
+      </c>
+      <c r="M1" t="s">
+        <v>566</v>
+      </c>
+      <c r="N1" t="s">
+        <v>648</v>
+      </c>
+      <c r="O1" t="s">
+        <v>649</v>
+      </c>
+      <c r="P1" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>650</v>
+      </c>
+      <c r="R1" t="s">
+        <v>651</v>
+      </c>
+      <c r="S1" t="s">
+        <v>565</v>
+      </c>
+      <c r="T1" t="s">
+        <v>652</v>
+      </c>
+      <c r="U1" t="s">
+        <v>653</v>
+      </c>
+      <c r="V1" t="s">
+        <v>654</v>
+      </c>
+      <c r="W1" t="s">
+        <v>655</v>
+      </c>
+      <c r="X1" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>569</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>571</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>572</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>570</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>579</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>582</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>590</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>591</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>594</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>575</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>595</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>656</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>657</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>658</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>659</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>660</v>
+      </c>
+      <c r="AR1" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="AS1" t="s">
+        <v>661</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>662</v>
       </c>
       <c r="C2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G2" t="s">
         <v>151</v>
       </c>
-      <c r="D2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" t="s">
-        <v>308</v>
+      <c r="H2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" t="s">
+        <v>600</v>
+      </c>
+      <c r="L2" t="s">
+        <v>666</v>
+      </c>
+      <c r="M2" t="s">
+        <v>667</v>
+      </c>
+      <c r="N2" t="s">
+        <v>156</v>
+      </c>
+      <c r="O2" t="s">
+        <v>668</v>
+      </c>
+      <c r="P2" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>669</v>
+      </c>
+      <c r="R2" t="s">
+        <v>191</v>
+      </c>
+      <c r="S2" t="s">
+        <v>602</v>
+      </c>
+      <c r="T2" t="s">
+        <v>670</v>
+      </c>
+      <c r="U2" t="s">
+        <v>671</v>
+      </c>
+      <c r="V2" t="s">
+        <v>672</v>
+      </c>
+      <c r="W2" t="s">
+        <v>673</v>
+      </c>
+      <c r="X2" t="s">
+        <v>674</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>675</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>676</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>609</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>610</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>677</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>373</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>619</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>678</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>315</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>679</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>678</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>668</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>678</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>680</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>677</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>681</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>668</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>682</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>683</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>684</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:D4" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>